--- a/Calculator_Test_Cases.xlsx
+++ b/Calculator_Test_Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myoffice.accenture.com/personal/keno_waldeck_accenture_com/Documents/Desktop/Kickstart/Coding/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="255" documentId="8_{D3639B9E-707B-4102-92BB-543116F8B696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B40E1679-C11B-410B-B578-73C5BF530173}"/>
+  <xr:revisionPtr revIDLastSave="168" documentId="8_{D3639B9E-707B-4102-92BB-543116F8B696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D54734CA-0BBB-4E52-A674-63365C488577}"/>
   <bookViews>
     <workbookView xWindow="-24765" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="101">
   <si>
     <t>Test ID</t>
   </si>
@@ -289,6 +289,9 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
+    <t>UT-09</t>
+  </si>
+  <si>
     <t>Rejects division by zero</t>
   </si>
   <si>
@@ -301,6 +304,9 @@
     <t>Cannot divide by zero.</t>
   </si>
   <si>
+    <t>UT-10</t>
+  </si>
+  <si>
     <t>Rejects empty first input</t>
   </si>
   <si>
@@ -313,6 +319,9 @@
     <t>Please enter a valid number in both fields.</t>
   </si>
   <si>
+    <t>UT-11</t>
+  </si>
+  <si>
     <t>Rejects empty second input</t>
   </si>
   <si>
@@ -322,6 +331,9 @@
     <t>Call validateInputs("2", "", "add")</t>
   </si>
   <si>
+    <t>UT-12</t>
+  </si>
+  <si>
     <t>Rejects non-numeric input</t>
   </si>
   <si>
@@ -331,6 +343,9 @@
     <t>Call validateInputs("abc", "3", "add")</t>
   </si>
   <si>
+    <t>UT-13</t>
+  </si>
+  <si>
     <t>Accepts valid numeric input</t>
   </si>
   <si>
@@ -343,23 +358,17 @@
     <t>null (no validation error)</t>
   </si>
   <si>
-    <t>Blocked</t>
-  </si>
-  <si>
-    <t>Unit Test Cases passed %:</t>
-  </si>
-  <si>
-    <t>Manual Test Cases passed %:</t>
-  </si>
-  <si>
-    <t>Total Test Cases passed %:</t>
+    <t>% Counter</t>
+  </si>
+  <si>
+    <t>mind. 80%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -389,16 +398,8 @@
       <color rgb="FF0000FF"/>
       <name val="Aptos"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -421,20 +422,8 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -462,109 +451,78 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="105">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
+  <dxfs count="58">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -579,6 +537,44 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -590,6 +586,44 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -599,30 +633,12 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -637,6 +653,34 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -648,11 +692,39 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -667,26 +739,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFE7E6E6"/>
@@ -711,382 +763,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1138,30 +814,6 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF2F5597"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1177,6 +829,16 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1192,6 +854,16 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1210,6 +882,16 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1228,6 +910,16 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1246,6 +938,16 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1264,6 +966,16 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1282,21 +994,25 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1314,80 +1030,46 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF2F5597"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -1418,6 +1100,9 @@
           <color theme="4" tint="0.39997558519241921"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1437,33 +1122,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ManualTestCases" displayName="ManualTestCases" ref="A2:H13" headerRowDxfId="86" dataDxfId="84" totalsRowDxfId="85">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ManualTestCases" displayName="ManualTestCases" ref="A2:H13" headerRowDxfId="57" dataDxfId="44">
   <autoFilter ref="A2:H13" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Test ID" dataDxfId="94"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Requirement" dataDxfId="93"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Test Case" dataDxfId="92"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Procedure" dataDxfId="91"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Expected Result" dataDxfId="90"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Actual Result" dataDxfId="89"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Status" dataDxfId="88"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Comments" dataDxfId="87"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Test ID" dataDxfId="52"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Requirement" dataDxfId="51"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Test Case" dataDxfId="50"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Procedure" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Expected Result" dataDxfId="48"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Actual Result" dataDxfId="47"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Status" dataDxfId="46"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Comments" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E9E57C70-9757-4EF8-88A5-9626B869E39B}" name="UnitTestCases" displayName="UnitTestCases" ref="J2:P15" totalsRowShown="0" headerRowDxfId="76" dataDxfId="75" headerRowBorderDxfId="103" tableBorderDxfId="104" totalsRowBorderDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E9E57C70-9757-4EF8-88A5-9626B869E39B}" name="UnitTestCases" displayName="UnitTestCases" ref="J2:P15" totalsRowShown="0" headerRowDxfId="53" dataDxfId="36" headerRowBorderDxfId="55" tableBorderDxfId="56" totalsRowBorderDxfId="54">
   <autoFilter ref="J2:P15" xr:uid="{E9E57C70-9757-4EF8-88A5-9626B869E39B}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{A3D28E3B-2041-49D8-99E7-E4F1F92B7332}" name="Test ID" dataDxfId="83"/>
-    <tableColumn id="2" xr3:uid="{B61E4D15-0EE6-4FF7-9DA6-E619F1844878}" name="Requirement" dataDxfId="82"/>
-    <tableColumn id="3" xr3:uid="{DB89AEDB-2AEA-4FD2-99EA-8B67866F8FA0}" name="Test name" dataDxfId="81"/>
-    <tableColumn id="4" xr3:uid="{726FFA9B-452C-4C29-9561-21D0B436483F}" name="Inputs" dataDxfId="80"/>
-    <tableColumn id="5" xr3:uid="{A1442B97-AA73-484A-A8D2-6AD637A9F00F}" name="Action" dataDxfId="79"/>
-    <tableColumn id="6" xr3:uid="{4F31538E-D9B8-4D20-814C-8C7B3ACCCF0B}" name="Expected result" dataDxfId="78"/>
-    <tableColumn id="7" xr3:uid="{86AF509B-B251-4D66-826A-9B6CE3D0E03F}" name="Status" dataDxfId="77"/>
+    <tableColumn id="1" xr3:uid="{A3D28E3B-2041-49D8-99E7-E4F1F92B7332}" name="Test ID" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{B61E4D15-0EE6-4FF7-9DA6-E619F1844878}" name="Requirement" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{DB89AEDB-2AEA-4FD2-99EA-8B67866F8FA0}" name="Test name" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{726FFA9B-452C-4C29-9561-21D0B436483F}" name="Inputs" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{A1442B97-AA73-484A-A8D2-6AD637A9F00F}" name="Action" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{4F31538E-D9B8-4D20-814C-8C7B3ACCCF0B}" name="Expected result" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{86AF509B-B251-4D66-826A-9B6CE3D0E03F}" name="Status" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1757,740 +1442,948 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="84.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="49.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7265625" style="1"/>
-    <col min="10" max="10" width="9.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="34.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.7265625" style="1"/>
-    <col min="18" max="18" width="26.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="6" width="42" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="13" max="13" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29.6328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="34.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="J1" s="5" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="J1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="R1" s="11" t="s">
-        <v>97</v>
-      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:18" s="4" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="R2" s="12"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
+    <row r="3" spans="1:18" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="7">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="7"/>
-      <c r="J3" s="2">
+      <c r="H3" s="10"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="11">
         <v>12</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" s="11">
         <v>5</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="R3" s="13">
-        <f>IFERROR((COUNTIF(G3:G13,"Pass")+COUNTIF(P3:P15,"Pass"))/(COUNTA(G3:G13)+COUNTA(P3:P15)),0)</f>
-        <v>0.875</v>
-      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A4" s="3">
+    <row r="4" spans="1:18" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H4" s="7"/>
-      <c r="J4" s="3">
+      <c r="G4" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="10"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="12">
         <v>13</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="O4" s="3">
+      <c r="O4" s="12">
         <v>5</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="9" t="s">
         <v>46</v>
       </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A5" s="3">
+    <row r="5" spans="1:18" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="7" t="s">
+      <c r="E5" s="8">
+        <v>8</v>
+      </c>
+      <c r="F5" s="8">
+        <v>8</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="H5" s="7"/>
-      <c r="J5" s="2">
+      <c r="H5" s="10"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="11">
         <v>14</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="O5" s="2">
+      <c r="O5" s="11">
         <v>2</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="P5" s="9" t="s">
         <v>46</v>
       </c>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A6" s="3">
+    <row r="6" spans="1:18" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="7">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H6" s="7"/>
-      <c r="J6" s="3">
+      <c r="E6" s="8">
+        <v>5</v>
+      </c>
+      <c r="F6" s="8">
+        <v>5</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="10"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="12">
         <v>15</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="L6" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="M6" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="N6" s="3" t="s">
+      <c r="N6" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="O6" s="3">
+      <c r="O6" s="12">
         <v>-2</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="P6" s="9" t="s">
         <v>46</v>
       </c>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A7" s="3">
+    <row r="7" spans="1:18" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="7">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="7" t="s">
+      <c r="E7" s="8">
+        <v>12</v>
+      </c>
+      <c r="F7" s="8">
+        <v>12</v>
+      </c>
+      <c r="G7" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="J7" s="2">
+      <c r="I7" s="6"/>
+      <c r="J7" s="11">
         <v>16</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="L7" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="N7" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="O7" s="2">
+      <c r="O7" s="11">
         <v>5</v>
       </c>
-      <c r="P7" s="7" t="s">
+      <c r="P7" s="9" t="s">
         <v>46</v>
       </c>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A8" s="3">
+    <row r="8" spans="1:18" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="7">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="7" t="s">
+      <c r="E8" s="8">
+        <v>5</v>
+      </c>
+      <c r="F8" s="8">
+        <v>12</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="7"/>
-      <c r="J8" s="3">
+      <c r="H8" s="10"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="12">
         <v>17</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="L8" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="M8" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="N8" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="12">
         <v>6</v>
       </c>
-      <c r="P8" s="7" t="s">
+      <c r="P8" s="9" t="s">
         <v>46</v>
       </c>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A9" s="3">
+    <row r="9" spans="1:18" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="7">
         <v>7</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="7"/>
-      <c r="J9" s="2">
+      <c r="H9" s="10"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="11">
         <v>18</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="L9" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M9" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="N9" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="O9" s="2">
+      <c r="O9" s="11">
         <v>0</v>
       </c>
-      <c r="P9" s="7" t="s">
+      <c r="P9" s="9" t="s">
         <v>46</v>
       </c>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A10" s="3">
+    <row r="10" spans="1:18" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="7">
         <v>8</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="7"/>
-      <c r="J10" s="3">
+      <c r="H10" s="10"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="13">
         <v>19</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="K10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="L10" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="M10" s="3" t="s">
+      <c r="M10" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="N10" s="3" t="s">
+      <c r="N10" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="12">
         <v>2</v>
       </c>
-      <c r="P10" s="7" t="s">
+      <c r="P10" s="9" t="s">
         <v>46</v>
       </c>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A11" s="3">
+      <c r="A11" s="7">
         <v>9</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="H11" s="7"/>
-      <c r="J11" s="3">
-        <v>20</v>
-      </c>
-      <c r="K11" s="3" t="s">
+      <c r="H11" s="10"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="L11" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M11" s="3" t="s">
+      <c r="L11" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="N11" s="3" t="s">
+      <c r="M11" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="N11" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="P11" s="7" t="s">
+      <c r="O11" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="P11" s="9" t="s">
         <v>46</v>
       </c>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A12" s="3">
+      <c r="A12" s="7">
         <v>10</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H12" s="7"/>
-      <c r="J12" s="3">
-        <v>21</v>
-      </c>
-      <c r="K12" s="3" t="s">
+      <c r="G12" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="10"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="K12" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="N12" s="3" t="s">
+      <c r="L12" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="O12" s="3" t="s">
+      <c r="M12" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="P12" s="7" t="s">
+      <c r="N12" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="O12" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="P12" s="9" t="s">
         <v>46</v>
       </c>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A13" s="3">
+      <c r="A13" s="7">
         <v>11</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="H13" s="7"/>
-      <c r="J13" s="3">
-        <v>22</v>
-      </c>
-      <c r="K13" s="3" t="s">
+      <c r="H13" s="10"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="K13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="L13" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="M13" s="3" t="s">
+      <c r="L13" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="M13" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="O13" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="N13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="P13" s="7" t="s">
+      <c r="P13" s="9" t="s">
         <v>46</v>
       </c>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="F14" s="3"/>
-      <c r="J14" s="3">
-        <v>23</v>
-      </c>
-      <c r="K14" s="3" t="s">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="K14" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="P14" s="7" t="s">
+      <c r="L14" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="M14" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="O14" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="P14" s="9" t="s">
         <v>46</v>
       </c>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="F15" s="9" t="s">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="M15" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="G15" s="10">
-        <f>COUNTIF(ManualTestCases[Status],"Pass")/COUNTA(ManualTestCases[Status])</f>
-        <v>0.72727272727272729</v>
-      </c>
-      <c r="J15" s="3">
-        <v>24</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="P15" s="7" t="s">
+      <c r="N15" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="O15" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="P15" s="9" t="s">
         <v>46</v>
       </c>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="P16" s="7"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
     </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="O17" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="P17" s="10">
-        <f>COUNTIF(ManualTestCases[Status],"Pass")/COUNTA(ManualTestCases[Status])</f>
-        <v>0.72727272727272729</v>
-      </c>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="P18" s="7"/>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
     </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="C23" s="8"/>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="6"/>
+      <c r="R19" s="6"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="6"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="J1:P1"/>
-    <mergeCell ref="R1:R2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G3:G13 P3:P14">
-    <cfRule type="expression" dxfId="49" priority="47">
+  <conditionalFormatting sqref="G3:G13">
+    <cfRule type="expression" dxfId="20" priority="43">
       <formula>$G3="Pass"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="48">
+    <cfRule type="expression" dxfId="19" priority="44">
       <formula>$G3="Fail"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="49">
+    <cfRule type="expression" dxfId="18" priority="45">
       <formula>$G3="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="50">
+    <cfRule type="expression" dxfId="17" priority="46">
       <formula>$G3="Not Run"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G1048576 G1:G14">
-    <cfRule type="containsText" dxfId="45" priority="12" operator="containsText" text="Blocked">
+  <conditionalFormatting sqref="G1:G1048576">
+    <cfRule type="containsText" dxfId="16" priority="10" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH("Pass",G1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="15" priority="9" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH("Fail",G1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="14" priority="8" operator="containsText" text="Blocked">
       <formula>NOT(ISERROR(SEARCH("Blocked",G1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="13" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH("Fail",G1)))</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3:P18">
+    <cfRule type="expression" dxfId="6" priority="4">
+      <formula>$G3="Pass"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="43" priority="14" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH("Pass",G1)))</formula>
+    <cfRule type="expression" dxfId="5" priority="5">
+      <formula>$G3="Fail"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="6">
+      <formula>$G3="Blocked"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="7">
+      <formula>$G3="Not Run"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P16 P18">
-    <cfRule type="containsText" dxfId="42" priority="5" operator="containsText" text="Blocked">
+  <conditionalFormatting sqref="P3:P18">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Blocked">
       <formula>NOT(ISERROR(SEARCH("Blocked",P3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="41" priority="6" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH("Fail",P3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="7" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH("Pass",P3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P18">
-    <cfRule type="expression" dxfId="39" priority="61">
-      <formula>$G18="Pass"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="38" priority="62">
-      <formula>$G18="Fail"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="63">
-      <formula>$G18="Blocked"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="64">
-      <formula>$G18="Not Run"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P16">
-    <cfRule type="expression" dxfId="32" priority="75">
-      <formula>$G15="Pass"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="31" priority="76">
-      <formula>$G15="Fail"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="77">
-      <formula>$G15="Blocked"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="29" priority="78">
-      <formula>$G15="Not Run"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P15">
-    <cfRule type="expression" dxfId="28" priority="79">
-      <formula>#REF!="Pass"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="80">
-      <formula>#REF!="Fail"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="81">
-      <formula>#REF!="Blocked"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="25" priority="82">
-      <formula>#REF!="Not Run"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/Calculator_Test_Cases.xlsx
+++ b/Calculator_Test_Cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myoffice.accenture.com/personal/keno_waldeck_accenture_com/Documents/Desktop/Kickstart/Coding/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myoffice.accenture.com/personal/keno_waldeck_accenture_com/Documents/Desktop/Kickstart/Coding/vitestTestProject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="168" documentId="8_{D3639B9E-707B-4102-92BB-543116F8B696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D54734CA-0BBB-4E52-A674-63365C488577}"/>
+  <xr:revisionPtr revIDLastSave="169" documentId="8_{D3639B9E-707B-4102-92BB-543116F8B696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A87DE00-1DFA-484C-B73E-1CAF2599B2CB}"/>
   <bookViews>
     <workbookView xWindow="-24765" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="99">
   <si>
     <t>Test ID</t>
   </si>
@@ -356,12 +356,6 @@
   </si>
   <si>
     <t>null (no validation error)</t>
-  </si>
-  <si>
-    <t>% Counter</t>
-  </si>
-  <si>
-    <t>mind. 80%</t>
   </si>
 </sst>
 </file>
@@ -464,12 +458,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -479,7 +469,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -501,11 +490,63 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="58">
+  <dxfs count="36">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -517,6 +558,44 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -528,44 +607,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -573,244 +614,6 @@
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF666666"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1006,13 +809,27 @@
       </border>
     </dxf>
     <dxf>
-      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1030,22 +847,14 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1072,34 +881,46 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF666666"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1117,38 +938,34 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ManualTestCases" displayName="ManualTestCases" ref="A2:H13" headerRowDxfId="57" dataDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ManualTestCases" displayName="ManualTestCases" ref="A2:H13" headerRowDxfId="35" dataDxfId="34">
   <autoFilter ref="A2:H13" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Test ID" dataDxfId="52"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Requirement" dataDxfId="51"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Test Case" dataDxfId="50"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Procedure" dataDxfId="49"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Expected Result" dataDxfId="48"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Actual Result" dataDxfId="47"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Status" dataDxfId="46"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Comments" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Test ID" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Requirement" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Test Case" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Procedure" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Expected Result" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Actual Result" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Status" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Comments" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E9E57C70-9757-4EF8-88A5-9626B869E39B}" name="UnitTestCases" displayName="UnitTestCases" ref="J2:P15" totalsRowShown="0" headerRowDxfId="53" dataDxfId="36" headerRowBorderDxfId="55" tableBorderDxfId="56" totalsRowBorderDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E9E57C70-9757-4EF8-88A5-9626B869E39B}" name="UnitTestCases" displayName="UnitTestCases" ref="J2:P15" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22" totalsRowBorderDxfId="21">
   <autoFilter ref="J2:P15" xr:uid="{E9E57C70-9757-4EF8-88A5-9626B869E39B}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{A3D28E3B-2041-49D8-99E7-E4F1F92B7332}" name="Test ID" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{B61E4D15-0EE6-4FF7-9DA6-E619F1844878}" name="Requirement" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{DB89AEDB-2AEA-4FD2-99EA-8B67866F8FA0}" name="Test name" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{726FFA9B-452C-4C29-9561-21D0B436483F}" name="Inputs" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{A1442B97-AA73-484A-A8D2-6AD637A9F00F}" name="Action" dataDxfId="39"/>
-    <tableColumn id="6" xr3:uid="{4F31538E-D9B8-4D20-814C-8C7B3ACCCF0B}" name="Expected result" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{86AF509B-B251-4D66-826A-9B6CE3D0E03F}" name="Status" dataDxfId="37"/>
+    <tableColumn id="1" xr3:uid="{A3D28E3B-2041-49D8-99E7-E4F1F92B7332}" name="Test ID" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{B61E4D15-0EE6-4FF7-9DA6-E619F1844878}" name="Requirement" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{DB89AEDB-2AEA-4FD2-99EA-8B67866F8FA0}" name="Test name" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{726FFA9B-452C-4C29-9561-21D0B436483F}" name="Inputs" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{A1442B97-AA73-484A-A8D2-6AD637A9F00F}" name="Action" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{4F31538E-D9B8-4D20-814C-8C7B3ACCCF0B}" name="Expected result" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{86AF509B-B251-4D66-826A-9B6CE3D0E03F}" name="Status" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1442,7 +1259,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1461,929 +1278,678 @@
     <col min="16" max="16" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="J1" s="2" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="J1" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
     </row>
-    <row r="2" spans="1:18" s="4" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:16" s="2" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="52" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="7">
+    <row r="3" spans="1:16" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H3" s="10"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="11">
+      <c r="G3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" s="7"/>
+      <c r="J3" s="8">
         <v>12</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="N3" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="O3" s="11">
+      <c r="O3" s="8">
         <v>5</v>
       </c>
-      <c r="P3" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
+      <c r="P3" s="6" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="4" spans="1:18" ht="52" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="7">
+    <row r="4" spans="1:16" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="12">
+      <c r="G4" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="7"/>
+      <c r="J4" s="9">
         <v>13</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="L4" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="N4" s="12" t="s">
+      <c r="N4" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="O4" s="12">
+      <c r="O4" s="9">
         <v>5</v>
       </c>
-      <c r="P4" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
+      <c r="P4" s="6" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="5" spans="1:18" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="7">
+    <row r="5" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
         <v>3</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="5">
         <v>8</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="5">
         <v>8</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="10"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="11">
+      <c r="G5" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="7"/>
+      <c r="J5" s="8">
         <v>14</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="L5" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="M5" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="N5" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="O5" s="11">
+      <c r="O5" s="8">
         <v>2</v>
       </c>
-      <c r="P5" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
+      <c r="P5" s="6" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="6" spans="1:18" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="7">
+    <row r="6" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="5">
         <v>5</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="5">
         <v>5</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" s="10"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="12">
+      <c r="G6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="J6" s="9">
         <v>15</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="L6" s="12" t="s">
+      <c r="L6" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M6" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="N6" s="12" t="s">
+      <c r="N6" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="O6" s="12">
+      <c r="O6" s="9">
         <v>-2</v>
       </c>
-      <c r="P6" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
+      <c r="P6" s="6" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="7" spans="1:18" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="7">
+    <row r="7" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
         <v>5</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="5">
         <v>12</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="5">
         <v>12</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" s="10" t="s">
+      <c r="G7" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="I7" s="6"/>
-      <c r="J7" s="11">
+      <c r="J7" s="8">
         <v>16</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="L7" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="N7" s="11" t="s">
+      <c r="N7" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="O7" s="11">
+      <c r="O7" s="8">
         <v>5</v>
       </c>
-      <c r="P7" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
+      <c r="P7" s="6" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="8" spans="1:18" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="7">
+    <row r="8" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
         <v>6</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="5">
         <v>5</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="5">
         <v>12</v>
       </c>
-      <c r="G8" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" s="10"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="12">
+      <c r="G8" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="J8" s="9">
         <v>17</v>
       </c>
-      <c r="K8" s="12" t="s">
+      <c r="K8" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="L8" s="12" t="s">
+      <c r="L8" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="N8" s="12" t="s">
+      <c r="N8" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="O8" s="12">
+      <c r="O8" s="9">
         <v>6</v>
       </c>
-      <c r="P8" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
+      <c r="P8" s="6" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="9" spans="1:18" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="7">
+    <row r="9" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
         <v>7</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="10"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="11">
+      <c r="G9" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="J9" s="8">
         <v>18</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="L9" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M9" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="N9" s="11" t="s">
+      <c r="N9" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="O9" s="11">
+      <c r="O9" s="8">
         <v>0</v>
       </c>
-      <c r="P9" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
+      <c r="P9" s="6" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="10" spans="1:18" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="7">
+    <row r="10" spans="1:16" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
         <v>8</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="10"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="13">
+      <c r="G10" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="J10" s="10">
         <v>19</v>
       </c>
-      <c r="K10" s="13" t="s">
+      <c r="K10" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L10" s="13" t="s">
+      <c r="L10" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="M10" s="13" t="s">
+      <c r="M10" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="N10" s="13" t="s">
+      <c r="N10" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="O10" s="12">
+      <c r="O10" s="9">
         <v>2</v>
       </c>
-      <c r="P10" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
+      <c r="P10" s="6" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A11" s="7">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
         <v>9</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="10"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="12" t="s">
+      <c r="G11" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="J11" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="K11" s="12" t="s">
+      <c r="K11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L11" s="12" t="s">
+      <c r="L11" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="M11" s="12" t="s">
+      <c r="M11" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="N11" s="12" t="s">
+      <c r="N11" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="O11" s="11" t="s">
+      <c r="O11" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="P11" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
+      <c r="P11" s="6" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A12" s="7">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
         <v>10</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H12" s="10"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="12" t="s">
+      <c r="G12" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="J12" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="K12" s="12" t="s">
+      <c r="K12" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L12" s="12" t="s">
+      <c r="L12" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="M12" s="12" t="s">
+      <c r="M12" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="N12" s="12" t="s">
+      <c r="N12" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="O12" s="12" t="s">
+      <c r="O12" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="P12" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
+      <c r="P12" s="6" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A13" s="7">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
         <v>11</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H13" s="10"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="12" t="s">
+      <c r="G13" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" s="7"/>
+      <c r="J13" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="K13" s="12" t="s">
+      <c r="K13" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L13" s="12" t="s">
+      <c r="L13" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="M13" s="12" t="s">
+      <c r="M13" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="N13" s="12" t="s">
+      <c r="N13" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="O13" s="11" t="s">
+      <c r="O13" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="P13" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
+      <c r="P13" s="6" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="12" t="s">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="F14" s="5"/>
+      <c r="J14" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="K14" s="12" t="s">
+      <c r="K14" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L14" s="12" t="s">
+      <c r="L14" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="M14" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="N14" s="12" t="s">
+      <c r="N14" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="O14" s="12" t="s">
+      <c r="O14" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="P14" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
+      <c r="P14" s="6" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="13" t="s">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="J15" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="K15" s="13" t="s">
+      <c r="K15" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="L15" s="13" t="s">
+      <c r="L15" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="M15" s="13" t="s">
+      <c r="M15" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="N15" s="13" t="s">
+      <c r="N15" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="O15" s="11" t="s">
+      <c r="O15" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="P15" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="6"/>
+      <c r="P15" s="6" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="6"/>
-      <c r="R17" s="6"/>
+    <row r="17" spans="16:16" x14ac:dyDescent="0.35">
+      <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
-      <c r="R19" s="6"/>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="6"/>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-      <c r="Q21" s="6"/>
-      <c r="R21" s="6"/>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="6"/>
-      <c r="R23" s="6"/>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="6"/>
+    <row r="18" spans="16:16" x14ac:dyDescent="0.35">
+      <c r="P18" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="J1:P1"/>
   </mergeCells>
+  <conditionalFormatting sqref="G1:G1048576">
+    <cfRule type="containsText" dxfId="13" priority="8" operator="containsText" text="Blocked">
+      <formula>NOT(ISERROR(SEARCH("Blocked",G1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="9" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH("Fail",G1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="11" priority="10" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH("Pass",G1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G3:G13">
-    <cfRule type="expression" dxfId="20" priority="43">
+    <cfRule type="expression" dxfId="10" priority="43">
       <formula>$G3="Pass"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="44">
+    <cfRule type="expression" dxfId="9" priority="44">
       <formula>$G3="Fail"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="45">
+    <cfRule type="expression" dxfId="8" priority="45">
       <formula>$G3="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="46">
-      <formula>$G3="Not Run"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="containsText" dxfId="16" priority="10" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH("Pass",G1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="9" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH("Fail",G1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="8" operator="containsText" text="Blocked">
-      <formula>NOT(ISERROR(SEARCH("Blocked",G1)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P18">
-    <cfRule type="expression" dxfId="6" priority="4">
-      <formula>$G3="Pass"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="5">
-      <formula>$G3="Fail"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="6">
-      <formula>$G3="Blocked"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="7">
+    <cfRule type="expression" dxfId="7" priority="46">
       <formula>$G3="Not Run"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3:P18">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Blocked">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Blocked">
       <formula>NOT(ISERROR(SEARCH("Blocked",P3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH("Fail",P3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH("Pass",P3)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>$G3="Pass"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="5">
+      <formula>$G3="Fail"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="6">
+      <formula>$G3="Blocked"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="7">
+      <formula>$G3="Not Run"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/Calculator_Test_Cases.xlsx
+++ b/Calculator_Test_Cases.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myoffice.accenture.com/personal/keno_waldeck_accenture_com/Documents/Desktop/Kickstart/Coding/vitestTestProject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="169" documentId="8_{D3639B9E-707B-4102-92BB-543116F8B696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A87DE00-1DFA-484C-B73E-1CAF2599B2CB}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="8_{D3639B9E-707B-4102-92BB-543116F8B696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55B68FB7-04E8-4FB2-B687-176E767BE0DC}"/>
   <bookViews>
     <workbookView xWindow="-24765" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Manual Test Cases" sheetId="1" r:id="rId1"/>
+    <sheet name="Calculator Test Cases" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Manual Test Cases'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Calculator Test Cases'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -1262,23 +1262,23 @@
   <dimension ref="A1:P18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="44" customWidth="1"/>
-    <col min="5" max="6" width="42" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="24" customWidth="1"/>
-    <col min="13" max="13" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.6328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="34.36328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="30" customWidth="1"/>
+    <col min="1" max="1" width="4.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="23.5" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>47</v>
       </c>
@@ -1299,7 +1299,7 @@
       <c r="O1" s="12"/>
       <c r="P1" s="12"/>
     </row>
-    <row r="2" spans="1:16" s="2" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>53</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="N3" s="8" t="s">
         <v>55</v>
@@ -1391,7 +1391,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>7</v>
       </c>
@@ -1663,7 +1663,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>8</v>
       </c>
